--- a/Win-Series/WIN 1-158/Win 1-158_Crypto infection inhibition_TUFTS.xlsx
+++ b/Win-Series/WIN 1-158/Win 1-158_Crypto infection inhibition_TUFTS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddayao01/Library/CloudStorage/Box-Box/R01 Evaluation of CDPK1 inhibitors_Crypto in vitro/Data for Greg_January 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ddayao01/Library/CloudStorage/Box-Box/DD Shared Folder 2026/Cryptosporidium/R01 Evaluation of CDPK1 inhibitors_Crypto in vitro/Data for Greg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ADE5E4-1C9B-FE42-BC69-1930CE0F799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5077F37B-6452-374C-B767-39222E2E4970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14060" yWindow="540" windowWidth="28040" windowHeight="16300" xr2:uid="{54FBB44D-0A49-0E43-88E7-D7DBB30D6BBA}"/>
+    <workbookView xWindow="760" yWindow="540" windowWidth="28040" windowHeight="16300" activeTab="1" xr2:uid="{54FBB44D-0A49-0E43-88E7-D7DBB30D6BBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Win 1-158_Tu114" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>Well 1</t>
   </si>
@@ -73,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -87,6 +87,11 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -121,6 +126,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1094,51 +1100,205 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>25</v>
+      </c>
+      <c r="C22" s="5">
+        <v>95.246873399999998</v>
+      </c>
+      <c r="D22" s="5">
+        <v>96.7055048</v>
+      </c>
+      <c r="E22" s="5">
+        <v>96.479165499999993</v>
+      </c>
+      <c r="F22" s="1">
+        <v>96.345038431585607</v>
+      </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C23" s="5">
+        <v>96.328272600000005</v>
+      </c>
+      <c r="D23" s="5">
+        <v>95.749849699999999</v>
+      </c>
+      <c r="E23" s="5">
+        <v>96.076784399999994</v>
+      </c>
+      <c r="F23" s="1">
+        <v>93.922368951604469</v>
+      </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
+      <c r="B24" s="1">
+        <v>2.7777777777777781</v>
+      </c>
+      <c r="C24" s="5">
+        <v>89.789579799999998</v>
+      </c>
+      <c r="D24" s="5">
+        <v>92.530800999999997</v>
+      </c>
+      <c r="E24" s="5">
+        <v>91.927229400000002</v>
+      </c>
+      <c r="F24" s="1">
+        <v>91.608677683525585</v>
+      </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>0.92592592592592604</v>
+      </c>
+      <c r="C25" s="5">
+        <v>85.816066599999999</v>
+      </c>
+      <c r="D25" s="5">
+        <v>88.205204300000005</v>
+      </c>
+      <c r="E25" s="5">
+        <v>87.601632699999996</v>
+      </c>
+      <c r="F25" s="1">
+        <v>87.316612722451779</v>
+      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
+      <c r="B26" s="1">
+        <v>0.30864197530864201</v>
+      </c>
+      <c r="C26" s="5">
+        <v>76.435557399999993</v>
+      </c>
+      <c r="D26" s="5">
+        <v>83.074845400000001</v>
+      </c>
+      <c r="E26" s="5">
+        <v>71.632133100000004</v>
+      </c>
+      <c r="F26" s="1">
+        <v>78.254655255809595</v>
+      </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
+      <c r="B27" s="1">
+        <v>0.10288065843621401</v>
+      </c>
+      <c r="C27" s="5">
+        <v>54.103406900000003</v>
+      </c>
+      <c r="D27" s="5">
+        <v>60.692397300000003</v>
+      </c>
+      <c r="E27" s="5">
+        <v>38.184204999999999</v>
+      </c>
+      <c r="F27" s="1">
+        <v>55.008764363118758</v>
+      </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
+      <c r="B28" s="1">
+        <v>3.4293552812071339E-2</v>
+      </c>
+      <c r="C28" s="5">
+        <v>29.105481699999999</v>
+      </c>
+      <c r="D28" s="5">
+        <v>54.983615499999999</v>
+      </c>
+      <c r="E28" s="5">
+        <v>48.444922800000001</v>
+      </c>
+      <c r="F28" s="1">
+        <v>20.59679822013431</v>
+      </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
+      <c r="B29" s="1">
+        <v>1.1431184270690446E-2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>38.385395600000003</v>
+      </c>
+      <c r="D29" s="5">
+        <v>29.206077000000001</v>
+      </c>
+      <c r="E29" s="5">
+        <v>-27.655401000000001</v>
+      </c>
+      <c r="F29" s="1">
+        <v>11.643818965394386</v>
+      </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
+      <c r="B30" s="1">
+        <v>3.8103947568968156E-3</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-0.84676070000000003</v>
+      </c>
+      <c r="D30" s="5">
+        <v>20.8315205</v>
+      </c>
+      <c r="E30" s="5">
+        <v>17.335834800000001</v>
+      </c>
+      <c r="F30" s="1">
+        <v>3.1770501945261067</v>
+      </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5">
+        <v>12.7838987</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-12.792449</v>
+      </c>
+      <c r="E31" s="5">
+        <v>8.2991100000000002E-3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>-2.5148818131826012E-4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
